--- a/testAffichageML/ig/StructureDefinition-fr-lm-status-document.xlsx
+++ b/testAffichageML/ig/StructureDefinition-fr-lm-status-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="119">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T09:34:46+00:00</t>
+    <t>2026-05-18T13:21:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,10 +354,6 @@
   </si>
   <si>
     <t>fr-lm-status-document.subSection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-section
-</t>
   </si>
   <si>
     <t>Sous-sections</t>
@@ -1762,13 +1758,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="M11" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1819,7 +1815,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1836,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1865,10 +1861,10 @@
         <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1919,7 +1915,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1936,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1962,13 +1958,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2019,7 +2015,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
